--- a/Result/profitability/1733.xlsx
+++ b/Result/profitability/1733.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.61</v>
       </c>
       <c r="M2" t="n">
-        <v>0.47125</v>
+        <v>0.47625</v>
       </c>
       <c r="N2" t="n">
-        <v>31.6625</v>
+        <v>32.335</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>0.49625</v>
+        <v>0.49375</v>
       </c>
       <c r="N3" t="n">
-        <v>33.3</v>
+        <v>33.34625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5962499999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>34.39375</v>
+        <v>34.95875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.65625</v>
+        <v>0.66625</v>
       </c>
       <c r="N5" t="n">
-        <v>36.61</v>
+        <v>37.4575</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.745</v>
+        <v>0.76375</v>
       </c>
       <c r="N6" t="n">
-        <v>39.26374999999999</v>
+        <v>40.41375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0.795</v>
+        <v>0.7787500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>41.26875</v>
+        <v>41.70375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8325</v>
+        <v>0.7775</v>
       </c>
       <c r="N8" t="n">
-        <v>42.4275</v>
+        <v>42.40625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>1.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0.87125</v>
+        <v>0.8712500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>43.62125</v>
@@ -1902,7 +1902,7 @@
         <v>1.055</v>
       </c>
       <c r="N12" t="n">
-        <v>43.4475</v>
+        <v>43.44750000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1733</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>471</v>
+      </c>
+      <c r="D75" t="n">
+        <v>312</v>
+      </c>
+      <c r="E75" t="n">
+        <v>158</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="G75" t="n">
+        <v>45</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.48%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>45</v>
+      </c>
+      <c r="K75" t="n">
+        <v>37</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.935</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.4400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5432098765432098</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1699999999999946</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005029585798816405</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2758620689655173</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.780000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.252513966480447</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
